--- a/DATA/EVALUACIONES/Exp01-V3/metadata_prediccion.xlsx
+++ b/DATA/EVALUACIONES/Exp01-V3/metadata_prediccion.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Escalado MinMax</t>
+          <t>RobustScaler</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-07-30 22:34</t>
+          <t>2026-08-11 19:24</t>
         </is>
       </c>
     </row>
